--- a/SourceData/Datas/quest.xlsx
+++ b/SourceData/Datas/quest.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1349,7 +1349,6 @@
       <c r="I6" t="n">
         <v>20</v>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
         <v>0</v>
       </c>
@@ -1377,7 +1376,6 @@
       <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>1</v>
       </c>
@@ -1387,7 +1385,6 @@
       <c r="I7" t="n">
         <v>20</v>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>0</v>
       </c>
@@ -1461,7 +1458,6 @@
       <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>1</v>
       </c>
@@ -1471,7 +1467,6 @@
       <c r="I9" t="n">
         <v>20</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
         <v>0</v>
       </c>
@@ -1493,13 +1488,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>选中水壶，给刚种下的作物浇水。</t>
+          <t>选中水壶，给刚种下的作物浇水。完成后获得催熟剂。</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>5</v>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>1</v>
       </c>
@@ -1509,9 +1503,13 @@
       <c r="I10" t="n">
         <v>20</v>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>boost</t>
+        </is>
+      </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>1006</v>
@@ -1531,13 +1529,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>作物成熟后，空手点击地块收获。</t>
+          <t>把催熟剂拖到快捷栏，点作物催熟，再空手收获。</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>6</v>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>1</v>
       </c>
@@ -1573,13 +1570,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>选中鱼竿，到湖边或码头钓一条鱼。</t>
+          <t>先选鱼竿，跟着箭头走到西边码头，点击抛竿钓一条鱼。</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>7</v>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>1</v>
       </c>
@@ -1598,10 +1594,256 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="M12" t="n">
         <v>70</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>1009</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>去镇上报到</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>点击北侧路牌，前往微光溪谷镇向镇长报到。</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>enter_town</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I13" t="n">
+        <v>60</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1010</v>
+      </c>
+      <c r="M13" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>1010</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>镇长的茶</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>拜访镇长府，取得在溪谷定居的许可。</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>visit_mayor</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I14" t="n">
+        <v>80</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1011</v>
+      </c>
+      <c r="M14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>1011</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>日常补给</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>在镇上任意商店购买一件商品，熟悉市集。</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shop_buy</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>15</v>
+      </c>
+      <c r="I15" t="n">
+        <v>40</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1012</v>
+      </c>
+      <c r="M15" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1012</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>镇上的声音</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>到警察局或邮局的公告板接取一次委托。</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>accept_board</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>16</v>
+      </c>
+      <c r="I16" t="n">
+        <v>50</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1013</v>
+      </c>
+      <c r="M16" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1013</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>工匠的钉子</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>拜访木工坊，认识负责修缮的工匠。</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>visit_carpenter</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>17</v>
+      </c>
+      <c r="I17" t="n">
+        <v>40</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1014</v>
+      </c>
+      <c r="M17" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1014</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>破旧的钟楼</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>前往社区中心查看修复工程，开启下一章线索。</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>visit_community</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>18</v>
+      </c>
+      <c r="I18" t="n">
+        <v>100</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/SourceData/Datas/quest.xlsx
+++ b/SourceData/Datas/quest.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1109,6 +1109,26 @@
           <t>sort</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>intro_script</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>outro_script</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>unlock_map</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1183,6 +1203,26 @@
           <t>int</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1250,6 +1290,26 @@
           <t>c</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1315,6 +1375,26 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>排序</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>接取对白脚本</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>完成对白脚本</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>章节 farm|town|market|spring</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>解锁地图 town|mine</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1409,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>用手拔除院子里的杂草，收集草料。</t>
+          <t>用手拔除院子里的杂草，多收集一些草料。</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1341,7 +1421,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
         <v>9</v>
@@ -1357,6 +1437,11 @@
       </c>
       <c r="M6" t="n">
         <v>10</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>farm</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1370,20 +1455,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>选中锄头，把一块荒地开垦成可播种的田。</t>
+          <t>把锄头拖进快捷栏，多翻几块荒地，攒点泥土。</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1394,78 +1479,98 @@
       <c r="M7" t="n">
         <v>20</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>quest_1002</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>farm</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>1003</v>
+        <v>1030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>搓出种子</t>
+          <t>采集石料</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>走到工作台，用草料合成种子。</t>
+          <t>打开背包把锄头拖到快捷栏，挖开院子里的石子与岩石。</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>seed_from_grass</t>
+          <t>stone</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>seeds</t>
-        </is>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1004</v>
+        <v>1031</v>
       </c>
       <c r="M8" t="n">
         <v>30</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>quest_1030</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>farm</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>1004</v>
+        <v>1031</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>播种希望</t>
+          <t>打造水壶</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>选中种子，在翻好的田地上播种。</t>
+          <t>走到工作台，用石料与泥土制作水壶。</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>can_basic</t>
+        </is>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1474,241 +1579,301 @@
         <v>1005</v>
       </c>
       <c r="M9" t="n">
-        <v>40</v>
+        <v>35</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>quest_1031</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>farm</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>浇灌作物</t>
+          <t>搓出种子</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>选中水壶，给刚种下的作物浇水。完成后获得催熟剂。</t>
+          <t>走到工作台，用草料合成种子。</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>seed_from_grass</t>
+        </is>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>boost</t>
+          <t>seeds</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="M10" t="n">
-        <v>50</v>
+        <v>25</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>quest_1003</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>farm</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>丰收时刻</t>
+          <t>播种希望</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>把催熟剂拖到快捷栏，点作物催熟，再空手收获。</t>
+          <t>打开背包把种子拖到快捷栏，在翻好的田地上多种几棵。</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>40</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>parsnip</t>
-        </is>
+        <v>25</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1007</v>
+        <v>1030</v>
       </c>
       <c r="M11" t="n">
-        <v>60</v>
+        <v>28</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>quest_1004</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>farm</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>湖边垂钓</t>
+          <t>浇灌作物</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>先选鱼竿，跟着箭头走到西边码头，点击抛竿钓一条鱼。</t>
+          <t>打开背包把水壶拖到快捷栏，给种下的作物浇水。完成后获得催熟剂。</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>boost</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1006</v>
+      </c>
+      <c r="M12" t="n">
         <v>50</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1009</v>
-      </c>
-      <c r="M12" t="n">
-        <v>70</v>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>quest_1005</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>farm</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>去镇上报到</t>
+          <t>丰收时刻</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>点击北侧路牌，前往微光溪谷镇向镇长报到。</t>
+          <t>把催熟剂拖到快捷栏，点作物催熟，再空手收获。</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>enter_town</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>40</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>parsnip</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="n">
-        <v>13</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="L13" t="n">
+        <v>1032</v>
+      </c>
+      <c r="M13" t="n">
         <v>60</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1010</v>
-      </c>
-      <c r="M13" t="n">
-        <v>90</v>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>quest_1006</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>farm</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>1010</v>
+        <v>1032</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>镇长的茶</t>
+          <t>打造斧头</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>拜访镇长府，取得在溪谷定居的许可。</t>
+          <t>走到工作台，用石料与草料制作斧头。</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>visit_mayor</t>
+          <t>axe_basic</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I14" t="n">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1011</v>
+        <v>1033</v>
       </c>
       <c r="M14" t="n">
-        <v>100</v>
+        <v>65</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>quest_1032</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>farm</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>1011</v>
+        <v>1033</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>日常补给</t>
+          <t>伐木练手</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>在镇上任意商店购买一件商品，熟悉市集。</t>
+          <t>打开背包把斧头拖到快捷栏，砍伐松树或橡树，收集木料。</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>shop_buy</t>
+          <t>wood</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I15" t="n">
         <v>40</v>
@@ -1717,106 +1882,141 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1012</v>
+        <v>1034</v>
       </c>
       <c r="M15" t="n">
-        <v>110</v>
+        <v>68</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>quest_1033</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>farm</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>1012</v>
+        <v>1034</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>镇上的声音</t>
+          <t>编织鱼竿</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>到警察局或邮局的公告板接取一次委托。</t>
+          <t>走到工作台，用木料与草料制作鱼竿。</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>accept_board</t>
+          <t>rod_basic</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="M16" t="n">
-        <v>120</v>
+        <v>69</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>quest_1034</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>farm</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>工匠的钉子</t>
+          <t>湖边垂钓</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>拜访木工坊，认识负责修缮的工匠。</t>
+          <t>打开背包把鱼竿拖到快捷栏，跟着箭头走到西边码头抛竿钓一条鱼。</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>visit_carpenter</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>40</v>
+        <v>50</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="M17" t="n">
-        <v>130</v>
+        <v>70</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>quest_1007</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>farm</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>破旧的钟楼</t>
+          <t>去镇上报到</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>前往社区中心查看修复工程，开启下一章线索。</t>
+          <t>点击东侧路牌，前往微光溪谷镇向镇长报到。</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1824,28 +2024,730 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>visit_community</t>
+          <t>enter_town</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I18" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>1010</v>
+      </c>
+      <c r="M18" t="n">
+        <v>90</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>quest_1009</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1010</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>镇长的茶</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>进入镇长府，与镇长·艾岚交谈，取得定居许可。</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>visit_mayor</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>14</v>
+      </c>
+      <c r="I19" t="n">
+        <v>80</v>
+      </c>
+      <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="M18" t="n">
+      <c r="L19" t="n">
+        <v>1011</v>
+      </c>
+      <c r="M19" t="n">
+        <v>100</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1011</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>镇上的声音</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>到警察局或邮局的公告板接取一次委托。</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>accept_board</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>50</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1012</v>
+      </c>
+      <c r="M20" t="n">
+        <v>110</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>quest_1011</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1012</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>工匠的钉子</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>拜访木工坊，认识负责修缮的工匠。</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>visit_carpenter</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>16</v>
+      </c>
+      <c r="I21" t="n">
+        <v>40</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1013</v>
+      </c>
+      <c r="M21" t="n">
+        <v>120</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>quest_1012</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1013</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>破旧的钟楼</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>前往社区中心查看修复工程，开启下一章线索。</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>visit_community</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>17</v>
+      </c>
+      <c r="I22" t="n">
+        <v>100</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1020</v>
+      </c>
+      <c r="M22" t="n">
+        <v>130</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>quest_1013</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>ch1_done</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1020</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>日常补给</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>在镇上任意商店购买一件商品，熟悉市集买卖。</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>shop_buy</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>18</v>
+      </c>
+      <c r="I23" t="n">
+        <v>40</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1021</v>
+      </c>
+      <c r="M23" t="n">
         <v>140</v>
       </c>
-    </row>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>quest_1020</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1021</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>出手盈余</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>在商店切换到「出售」，卖掉一件背包里的收获物。</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>shop_sell</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>19</v>
+      </c>
+      <c r="I24" t="n">
+        <v>40</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1022</v>
+      </c>
+      <c r="M24" t="n">
+        <v>150</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>quest_1021</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1022</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>春厅立项</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>回到社区中心，在春厅收集包上签字立项。</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>accept_spring_pack</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>20</v>
+      </c>
+      <c r="I25" t="n">
+        <v>60</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1023</v>
+      </c>
+      <c r="M25" t="n">
+        <v>160</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>quest_1022</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1023</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>诊所的叮嘱</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>拜访微光诊所，听医生说说矿洞安全。</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>visit_clinic</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>21</v>
+      </c>
+      <c r="I26" t="n">
+        <v>40</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1024</v>
+      </c>
+      <c r="M26" t="n">
+        <v>170</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>quest_1023</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1024</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>矿脉通行证</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>前往矿脉商会（矿石店），取得浅层矿洞放行。</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>visit_oreshop</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>22</v>
+      </c>
+      <c r="I27" t="n">
+        <v>50</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1025</v>
+      </c>
+      <c r="M27" t="n">
+        <v>180</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>quest_1024</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>mine</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1025</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>浅层铜脉</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>点击北山矿洞路牌，进入浅层矿洞。</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>enter_mine</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>23</v>
+      </c>
+      <c r="I28" t="n">
+        <v>40</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1026</v>
+      </c>
+      <c r="M28" t="n">
+        <v>190</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>quest_1025</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>mine</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1026</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>采一袋铜</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>在矿洞里选中锄头，挖取铜矿石。</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>copper</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>24</v>
+      </c>
+      <c r="I29" t="n">
+        <v>80</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1027</v>
+      </c>
+      <c r="M29" t="n">
+        <v>200</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>quest_1026</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>mine</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1027</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>春厅微光</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>把铜矿送回社区中心，点亮春厅的第一盏灯。</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>light_spring_hall</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>25</v>
+      </c>
+      <c r="I30" t="n">
+        <v>120</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>210</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>quest_1027</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>ch2_done</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>mine</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SourceData/Datas/quest.xlsx
+++ b/SourceData/Datas/quest.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>前往矿脉商会（矿石店），取得浅层矿洞放行。</t>
+          <t>前往矿脉商会，向掌柜·赤铜打听浅层矿洞放行。</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>mine</t>
+          <t>town</t>
         </is>
       </c>
     </row>
@@ -2738,16 +2738,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SourceData/Datas/quest.xlsx
+++ b/SourceData/Datas/quest.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="18400" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quest" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="quest" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>打开背包把水壶拖到快捷栏，给种下的作物浇水。完成后获得催熟剂。</t>
+          <t>选中水壶给作物浇水。完成后获得催熟剂；夜里睡一觉田才会熟。</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1729,7 +1729,7 @@
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>1006</v>
+        <v>1035</v>
       </c>
       <c r="M12" t="n">
         <v>50</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>把催熟剂拖到快捷栏，点作物催熟，再空手收获。</t>
+          <t>睡醒后空手点击成熟作物收获。也可用催熟剂跳过一晚。</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2735,6 +2735,57 @@
       <c r="Q30" t="inlineStr">
         <is>
           <t>mine</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1035</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>第一夜</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>天色不早了，点小屋门睡到明天。浇过水的作物会在夜里长大。</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>sleep_first</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>28</v>
+      </c>
+      <c r="I31" t="n">
+        <v>20</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1006</v>
+      </c>
+      <c r="M31" t="n">
+        <v>55</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>quest_1035</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>farm</t>
         </is>
       </c>
     </row>
